--- a/report/功能列表.xlsx
+++ b/report/功能列表.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="28480" windowHeight="14100"/>
   </bookViews>
   <sheets>
-    <sheet name="功能表" sheetId="1" r:id="rId1"/>
+    <sheet name="功能性需求" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
